--- a/artfynd/A 25725-2025 artfynd.xlsx
+++ b/artfynd/A 25725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130210099</v>
       </c>
       <c r="B2" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25725-2025 artfynd.xlsx
+++ b/artfynd/A 25725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130210099</v>
       </c>
       <c r="B2" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25725-2025 artfynd.xlsx
+++ b/artfynd/A 25725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130210099</v>
       </c>
       <c r="B2" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25725-2025 artfynd.xlsx
+++ b/artfynd/A 25725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130210099</v>
       </c>
       <c r="B2" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25725-2025 artfynd.xlsx
+++ b/artfynd/A 25725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130210099</v>
       </c>
       <c r="B2" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25725-2025 artfynd.xlsx
+++ b/artfynd/A 25725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130210099</v>
       </c>
       <c r="B2" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
